--- a/api/game_conf/excel/game_attribute.xlsx
+++ b/api/game_conf/excel/game_attribute.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J131"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,10 +489,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>道具配置ID</t>
@@ -525,10 +521,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>道具类型（0=普通/1=一级货币/2=二级货币/3=资源）</t>
@@ -561,10 +553,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>数量</t>
@@ -597,10 +585,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>道具配置ID（英雄卡时=英雄配置ID）</t>
@@ -633,10 +617,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>数量</t>
@@ -669,10 +649,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>等级</t>
@@ -705,10 +681,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>该等级数值</t>
@@ -741,10 +713,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>战斗回合数</t>
@@ -777,10 +745,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>第1回合受伤比例(%)</t>
@@ -813,10 +777,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>每回合受伤比例递减(%)</t>
@@ -849,10 +809,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>结算阶段每回合伤兵转死亡比例(%)</t>
@@ -885,10 +841,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>物理伤害收敛系数(%)</t>
@@ -921,10 +873,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>法术伤害收敛系数(%)</t>
@@ -957,10 +905,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>战斗经验系数</t>
@@ -993,10 +937,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>编队最大槽位数</t>
@@ -1029,10 +969,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>兵种转化所需等级</t>
@@ -1065,10 +1001,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>默认兵种配置ID</t>
@@ -1101,10 +1033,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>扩展兵种解锁道具配置ID</t>
@@ -1142,9 +1070,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>转化消耗（资源混搭）</t>
@@ -1177,10 +1102,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>英雄等级上限</t>
@@ -1213,10 +1134,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>每10级获得的自由属性点</t>
@@ -1249,10 +1166,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>星级上限</t>
@@ -1285,10 +1198,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>每升1星发放的自由属性点</t>
@@ -1321,10 +1230,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>觉醒等级门槛</t>
@@ -1362,9 +1267,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>觉醒消耗（资源混搭）</t>
@@ -1397,14 +1299,11 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>英雄等级（1~max_level）</t>
@@ -1437,10 +1336,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>从该级升到下一级所需经验</t>
@@ -1473,14 +1368,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>英雄配置ID</t>
@@ -1513,10 +1405,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>基础攻击（lv1）</t>
@@ -1549,10 +1437,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>基础防御（lv1）</t>
@@ -1585,10 +1469,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>基础智力（lv1）</t>
@@ -1621,10 +1501,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>基础移动（lv1）</t>
@@ -1657,10 +1533,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>基础拆迁（lv1）</t>
@@ -1693,10 +1565,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>每级攻击成长</t>
@@ -1729,10 +1597,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>每级防御成长</t>
@@ -1765,10 +1629,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>每级智力成长</t>
@@ -1801,10 +1661,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>每级移动成长</t>
@@ -1837,10 +1693,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>每级拆迁成长</t>
@@ -1873,10 +1725,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>攻击距离</t>
@@ -1909,14 +1757,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>道具配置ID</t>
@@ -1949,10 +1794,6 @@
           <t>itemeffecttype</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>道具效果类型</t>
@@ -1985,10 +1826,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>目标配置ID（货币/道具）</t>
@@ -2021,10 +1858,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>单个道具的效果数值</t>
@@ -2057,14 +1890,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>来源货币配置ID（一级货币）</t>
@@ -2097,10 +1927,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>来源货币类型（1=一级/2=二级）</t>
@@ -2133,10 +1959,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>目标货币配置ID（二级货币）</t>
@@ -2169,10 +1991,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>目标货币类型（1=一级/2=二级）</t>
@@ -2205,10 +2023,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>消耗来源货币数量（每组）</t>
@@ -2241,10 +2055,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>获得目标货币数量（每组）</t>
@@ -2277,14 +2087,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>资源地等级 1~9</t>
@@ -2317,10 +2124,6 @@
           <t>resourcetype</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>产出方式（type 为 Go/proto 保留字故用 res_type）</t>
@@ -2353,10 +2156,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>混合/单项产量</t>
@@ -2389,10 +2188,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>双资源主产量</t>
@@ -2425,10 +2220,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>双资源次级产量</t>
@@ -2461,14 +2252,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>抽卡池ID</t>
@@ -2501,10 +2289,6 @@
           <t>string</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>抽卡池名称</t>
@@ -2537,10 +2321,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>抽卡券道具配置ID（0=无券模式）</t>
@@ -2573,10 +2353,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>单抽消耗券数</t>
@@ -2609,10 +2385,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>单抽消耗金币数</t>
@@ -2645,10 +2417,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>十连消耗券数</t>
@@ -2681,10 +2449,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>十连消耗金币数</t>
@@ -2717,10 +2481,6 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>每日免费窗口各1次</t>
@@ -2753,10 +2513,6 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>半价窗口各1次</t>
@@ -2789,10 +2545,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>累抽N次必出高稀有度</t>
@@ -2825,10 +2577,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>保底命中时走的掉落组</t>
@@ -2861,10 +2609,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>首抽保底组（0=无）</t>
@@ -2902,9 +2646,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>心愿可选英雄配置ID集合</t>
@@ -2937,10 +2678,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>心愿进度阈值</t>
@@ -2973,10 +2710,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>归属抽卡池</t>
@@ -3009,10 +2742,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>组ID（档位）</t>
@@ -3045,10 +2774,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>非保底抽取时的组权重</t>
@@ -3081,10 +2806,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>归属抽卡池</t>
@@ -3117,10 +2838,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>归属掉落组</t>
@@ -3153,10 +2870,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>英雄或道具配置ID</t>
@@ -3189,10 +2902,6 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>true=英雄卡；false=道具</t>
@@ -3225,10 +2934,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>产出数量（英雄卡恒1）</t>
@@ -3261,10 +2966,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>组内权重</t>
@@ -3297,10 +2998,6 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>命中后保底计数归零</t>
@@ -3333,10 +3030,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>地块可开发的最高等级上限</t>
@@ -3369,14 +3062,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>地块等级（守军查表索引）</t>
@@ -3409,10 +3099,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>归属地块等级</t>
@@ -3445,10 +3131,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>守军英雄配置ID</t>
@@ -3481,10 +3163,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>固定兵力</t>
@@ -3517,10 +3195,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>英雄上阵默认兵力</t>
@@ -3553,14 +3227,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>英雄等级断点</t>
@@ -3593,10 +3264,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>该等级及以上的基础兵力</t>
@@ -3629,14 +3296,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>兵营等级断点</t>
@@ -3669,10 +3333,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>该等级的累计兵力加成</t>
@@ -3705,10 +3365,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>每天获得审查次数</t>
@@ -3741,10 +3397,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>最多累积次数</t>
@@ -3777,10 +3429,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>每次审查生成任务数</t>
@@ -3813,10 +3461,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>每次审查最低经验</t>
@@ -3849,10 +3493,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>每次审查最高经验</t>
@@ -3885,10 +3525,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>赛季天数</t>
@@ -3921,10 +3557,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>前N级每升1级送1次审查次数</t>
@@ -3957,14 +3589,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>审查等级</t>
@@ -3997,10 +3626,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>升到该等级所需累计经验</t>
@@ -4038,9 +3663,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>该等级任务奖励（道具）</t>
@@ -4073,14 +3695,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>技能配置ID</t>
@@ -4113,10 +3732,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>等级上限</t>
@@ -4149,10 +3764,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>可装配次数上限</t>
@@ -4185,10 +3796,6 @@
           <t>cost</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>单次升级消耗</t>
@@ -4221,10 +3828,6 @@
           <t>skilltype</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>技能类型</t>
@@ -4257,10 +3860,6 @@
           <t>targettype</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>目标选择</t>
@@ -4293,10 +3892,6 @@
           <t>effecttype</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>效果类型</t>
@@ -4329,10 +3924,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>技能伤害系数(%)，0=按基础攻/智算</t>
@@ -4365,10 +3956,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>技能收敛系数(%)，0=用战斗规则全局系数</t>
@@ -4401,10 +3988,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>追击触发概率(%)，仅追击技能有效</t>
@@ -4437,14 +4020,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>技能配置ID</t>
@@ -4482,9 +4062,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>所需英雄卡（ItemID=英雄配置ID）</t>
@@ -4517,10 +4094,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>index0 默认技能槽（英雄自带）</t>
@@ -4553,10 +4126,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>可装配槽位起始</t>
@@ -4589,10 +4158,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>可装配槽位上限</t>
@@ -4625,10 +4190,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>槽位1（index1）解锁所需英雄等级</t>
@@ -4661,10 +4222,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>槽位2（index2）解锁所需英雄等级</t>
@@ -4697,10 +4254,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>拆卸返还比例（每升1级返1/N）</t>
@@ -4733,14 +4286,11 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>建筑类型（BuildingType；type 为保留字故用 btype）</t>
@@ -4773,10 +4323,6 @@
           <t>string</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>建筑名称</t>
@@ -4809,10 +4355,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>占地格子数（4=2x2/9=3x3）</t>
@@ -4845,10 +4387,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>等级上限</t>
@@ -4881,10 +4419,6 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>建造耗时(秒)；0=即时</t>
@@ -4922,9 +4456,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>建造消耗（可空=免费）</t>
@@ -4962,9 +4493,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>1→2 升级消耗基数</t>
@@ -4997,10 +4525,6 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>升级消耗成长（每级乘数）</t>
@@ -5033,10 +4557,6 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>升级耗时成长（每级乘数）</t>
@@ -5074,9 +4594,6 @@
           <t>|</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>校场：等级→队列数断点</t>
@@ -5109,10 +4626,6 @@
           <t>uint32</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>城墙：每级防御加成</t>
@@ -5145,10 +4658,6 @@
           <t>uint64</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>仓库：每级资源存量上限</t>
@@ -5181,10 +4690,6 @@
           <t>int32</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>资源建筑：产出资源配置ID</t>
@@ -5217,13 +4722,829 @@
           <t>int64</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>资源建筑：每级每小时产出</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>英雄配置ID</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>conf_id</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>英雄配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>英雄名</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>英雄名</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>唯一名</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>unique_name</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>唯一名称（含阵营和兵种）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>阵营</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>阵营（群/魏/蜀/吴/汉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>性别</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>性别（男/女）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>品质</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>品质（3-R/4-SR/5-SSR）</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>图标ID</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>icon_id</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>图标ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>主兵种</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>troop_type</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>主兵种（骑/步/弓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>可用兵种</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>troop_available</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>可用兵种列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>部署消耗</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>deploy_cost</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>部署消耗</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>英雄描述（史实+演义）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>政策ID</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>policy_id</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>政策ID（引用 hero_policy）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>hero_base</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>羁绊组ID</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>group_id</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>羁绊组ID（引用 hero_group，空=无羁绊）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>hero_method</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>战法ID</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>method_id</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>战法ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>hero_method</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>战法名</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>method_name</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>战法名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>hero_method</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>战法描述</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>method_desc</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>战法效果描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>hero_method_slot</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>英雄配置ID</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>hero_conf_id</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>英雄配置ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>hero_method_slot</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>槽位索引</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>slot_index</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>槽位索引（0/1/2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>hero_method_slot</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>战法ID</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>method_id</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>战法ID（引用 hero_method）</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>hero_policy</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>政策ID</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>policy_id</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>int32</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>政策ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>hero_policy</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>政策名</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>policy_name</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>政策名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>hero_policy</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>政策描述</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>policy_desc</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>政策效果描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>hero_group</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>羁绊组ID</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>group_id</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>羁绊组ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>hero_group</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>羁绊名</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>羁绊组名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表头</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>hero_group</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>羁绊描述</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>group_desc</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>羁绊描述（成员+加成）</t>
         </is>
       </c>
     </row>
